--- a/docs/StructureDefinition-LTC-Composition-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-Composition-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-Composition-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-Composition-CS100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5520" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5520" uniqueCount="593">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -751,7 +751,7 @@
     <t>指定特定類型的composition（如病史和體檢、出院摘要、病程紀錄）。這通常等同於製作composition的目的。</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>For Composition type, LOINC is ubiquitous and strongly endorsed by HL7. Most implementation guides will require a specific LOINC code, or use LOINC as an extensible binding.</t>
   </si>
   <si>
     <t>描述composition的關鍵metadata資料項目，用於查詢/篩選。</t>
@@ -771,11 +771,19 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/loinc-type-doc-code</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.type</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Composition.category</t>
@@ -794,6 +802,15 @@
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/loinc-document-classcodes</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>DocumenttReference.category</t>
   </si>
   <si>
     <t>Composition.subject</t>
@@ -1178,7 +1195,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition)</t>
+Reference(Composition|4.0.1)</t>
   </si>
   <si>
     <t>此關係的目標文件</t>
@@ -1250,6 +1267,9 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
+    <t>DocumentReference.event.code</t>
+  </si>
+  <si>
     <t>Composition.event.period</t>
   </si>
   <si>
@@ -1265,7 +1285,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1344,6 +1364,10 @@
     <t>一個用於指明小節中所含內容種類的代碼，這個代碼必須與小節的標題相一致。</t>
   </si>
   <si>
+    <t>The code identifies the section for an automated processor of the document. This is particularly relevant when using profiles to control the structure of the document.   
+If the section has content (instead of sub-sections), the section.code does not change the meaning or interpretation of the resource that is the content of the section in the comments for the section.code.</t>
+  </si>
+  <si>
     <t>提供給文件中主題的標籤是標準化的，並且可以被電腦程式識別和處理。</t>
   </si>
   <si>
@@ -1414,9 +1438,6 @@
     <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Composition.section.orderedBy</t>
   </si>
   <si>
@@ -1436,6 +1457,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/list-order</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
   </si>
   <si>
     <t>Composition.section.entry</t>
@@ -1476,6 +1500,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
   </si>
   <si>
     <t>Composition.section.section</t>
@@ -4589,7 +4616,7 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>233</v>
@@ -4662,33 +4689,33 @@
         <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>20</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4708,22 +4735,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4754,7 +4781,7 @@
         <v>239</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4772,7 +4799,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4781,33 +4808,33 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>20</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4830,19 +4857,19 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4891,7 +4918,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4909,24 +4936,24 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4949,17 +4976,17 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5008,7 +5035,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5023,27 +5050,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5066,19 +5093,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5127,7 +5154,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -5142,27 +5169,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5185,17 +5212,17 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5244,7 +5271,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5259,27 +5286,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5305,13 +5332,13 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5361,7 +5388,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5379,13 +5406,13 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5393,10 +5420,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5422,13 +5449,13 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5457,10 +5484,10 @@
         <v>176</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5478,7 +5505,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5496,13 +5523,13 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5510,10 +5537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5536,19 +5563,19 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5597,7 +5624,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5615,13 +5642,13 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5629,10 +5656,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5744,10 +5771,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5861,14 +5888,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5890,16 +5917,16 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5948,7 +5975,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5980,10 +6007,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6009,14 +6036,14 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6044,10 +6071,10 @@
         <v>176</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -6065,7 +6092,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6083,10 +6110,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6097,10 +6124,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6123,17 +6150,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6182,7 +6209,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6200,10 +6227,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6214,10 +6241,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6240,17 +6267,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6299,7 +6326,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6317,24 +6344,24 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6357,19 +6384,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6418,7 +6445,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6436,13 +6463,13 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6450,10 +6477,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6476,16 +6503,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6535,7 +6562,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6553,13 +6580,13 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6567,10 +6594,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6682,10 +6709,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6799,14 +6826,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6828,16 +6855,16 @@
         <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6886,7 +6913,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6918,10 +6945,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6947,13 +6974,13 @@
         <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6982,10 +7009,10 @@
         <v>176</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -7003,7 +7030,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -7021,13 +7048,13 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7035,10 +7062,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7061,13 +7088,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7118,7 +7145,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>90</v>
@@ -7136,13 +7163,13 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7150,10 +7177,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7176,19 +7203,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7237,7 +7264,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7255,13 +7282,13 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7269,10 +7296,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7384,10 +7411,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7501,14 +7528,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7530,16 +7557,16 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7588,7 +7615,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7620,10 +7647,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7643,19 +7670,19 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>233</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7681,31 +7708,31 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7714,7 +7741,7 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -7723,13 +7750,13 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7737,10 +7764,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7766,10 +7793,10 @@
         <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7820,7 +7847,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7838,13 +7865,13 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7852,10 +7879,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7878,16 +7905,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7937,7 +7964,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7955,7 +7982,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>161</v>
@@ -7969,10 +7996,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7980,7 +8007,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>79</v>
@@ -7995,13 +8022,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8040,7 +8067,7 @@
         <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8050,7 +8077,7 @@
         <v>169</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8062,16 +8089,16 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8082,10 +8109,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8197,10 +8224,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8314,14 +8341,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8343,16 +8370,16 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8401,7 +8428,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8433,14 +8460,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8462,16 +8489,16 @@
         <v>157</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8520,7 +8547,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8538,10 +8565,10 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8552,10 +8579,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8581,16 +8608,16 @@
         <v>233</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8621,7 +8648,7 @@
         <v>239</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8639,7 +8666,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8648,7 +8675,7 @@
         <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>102</v>
@@ -8660,7 +8687,7 @@
         <v>242</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8671,10 +8698,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8697,17 +8724,17 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8756,7 +8783,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8774,24 +8801,24 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8814,16 +8841,16 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8873,7 +8900,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8894,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -8905,10 +8932,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8934,13 +8961,13 @@
         <v>121</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8990,7 +9017,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8999,7 +9026,7 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -9008,10 +9035,10 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
@@ -9022,10 +9049,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9051,16 +9078,16 @@
         <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9088,10 +9115,10 @@
         <v>176</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9109,7 +9136,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9127,7 +9154,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>161</v>
@@ -9136,15 +9163,15 @@
         <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9170,16 +9197,16 @@
         <v>233</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9207,10 +9234,10 @@
         <v>115</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9228,7 +9255,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9237,7 +9264,7 @@
         <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>102</v>
@@ -9246,10 +9273,10 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -9260,10 +9287,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9286,16 +9313,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9345,7 +9372,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9354,7 +9381,7 @@
         <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>102</v>
@@ -9363,10 +9390,10 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>20</v>
@@ -9377,10 +9404,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9406,16 +9433,16 @@
         <v>233</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9443,37 +9470,37 @@
         <v>115</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z62" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9482,10 +9509,10 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
@@ -9496,10 +9523,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9525,13 +9552,13 @@
         <v>80</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9581,7 +9608,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9590,7 +9617,7 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
@@ -9599,10 +9626,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9613,13 +9640,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>20</v>
@@ -9641,13 +9668,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9698,7 +9725,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9710,16 +9737,16 @@
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9730,10 +9757,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9845,10 +9872,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9962,14 +9989,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9991,16 +10018,16 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10049,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10081,14 +10108,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10110,16 +10137,16 @@
         <v>157</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10129,7 +10156,7 @@
         <v>20</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>20</v>
@@ -10168,7 +10195,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10186,10 +10213,10 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -10200,10 +10227,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10229,16 +10256,16 @@
         <v>233</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10248,7 +10275,7 @@
         <v>20</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>20</v>
@@ -10269,7 +10296,7 @@
         <v>239</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10287,7 +10314,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10296,7 +10323,7 @@
         <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>102</v>
@@ -10308,7 +10335,7 @@
         <v>242</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -10319,10 +10346,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10345,17 +10372,17 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10404,7 +10431,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10422,24 +10449,24 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10462,16 +10489,16 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10521,7 +10548,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10542,7 +10569,7 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -10553,10 +10580,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10582,13 +10609,13 @@
         <v>121</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10638,7 +10665,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10647,7 +10674,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -10656,10 +10683,10 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10670,10 +10697,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10699,16 +10726,16 @@
         <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10736,10 +10763,10 @@
         <v>176</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10757,7 +10784,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10775,7 +10802,7 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>161</v>
@@ -10784,15 +10811,15 @@
         <v>20</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10818,16 +10845,16 @@
         <v>233</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10855,10 +10882,10 @@
         <v>115</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -10876,7 +10903,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10885,7 +10912,7 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
@@ -10894,10 +10921,10 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>
@@ -10908,10 +10935,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10934,16 +10961,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10993,7 +11020,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11002,7 +11029,7 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>102</v>
@@ -11011,10 +11038,10 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>20</v>
@@ -11025,10 +11052,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11054,16 +11081,16 @@
         <v>233</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11091,37 +11118,37 @@
         <v>115</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI76" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>102</v>
@@ -11130,10 +11157,10 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>20</v>
@@ -11144,10 +11171,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11173,13 +11200,13 @@
         <v>80</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11229,7 +11256,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11238,7 +11265,7 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
@@ -11247,10 +11274,10 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>20</v>
@@ -11261,13 +11288,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>20</v>
@@ -11289,13 +11316,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11346,7 +11373,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11358,16 +11385,16 @@
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>20</v>
@@ -11378,10 +11405,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11493,10 +11520,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11610,14 +11637,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11639,16 +11666,16 @@
         <v>135</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11697,7 +11724,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11729,14 +11756,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11758,16 +11785,16 @@
         <v>157</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11777,7 +11804,7 @@
         <v>20</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>20</v>
@@ -11816,7 +11843,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11834,10 +11861,10 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>20</v>
@@ -11848,10 +11875,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11877,16 +11904,16 @@
         <v>233</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11896,7 +11923,7 @@
         <v>20</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>20</v>
@@ -11917,7 +11944,7 @@
         <v>239</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -11935,7 +11962,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11944,7 +11971,7 @@
         <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>102</v>
@@ -11956,7 +11983,7 @@
         <v>242</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>20</v>
@@ -11967,10 +11994,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11993,17 +12020,17 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12052,7 +12079,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12070,24 +12097,24 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12110,16 +12137,16 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12169,7 +12196,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12190,7 +12217,7 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>20</v>
@@ -12201,10 +12228,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12230,13 +12257,13 @@
         <v>121</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12286,7 +12313,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12295,7 +12322,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -12304,10 +12331,10 @@
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>20</v>
@@ -12318,10 +12345,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12347,16 +12374,16 @@
         <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12384,10 +12411,10 @@
         <v>176</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
@@ -12405,7 +12432,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12423,7 +12450,7 @@
         <v>20</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>161</v>
@@ -12432,15 +12459,15 @@
         <v>20</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12466,16 +12493,16 @@
         <v>233</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12503,10 +12530,10 @@
         <v>115</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12524,7 +12551,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12533,7 +12560,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -12542,10 +12569,10 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>20</v>
@@ -12556,10 +12583,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12582,16 +12609,16 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12641,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12650,7 +12677,7 @@
         <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -12659,10 +12686,10 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>20</v>
@@ -12673,10 +12700,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12702,16 +12729,16 @@
         <v>233</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12739,37 +12766,37 @@
         <v>115</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z90" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>102</v>
@@ -12778,10 +12805,10 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>20</v>
@@ -12792,10 +12819,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12821,13 +12848,13 @@
         <v>80</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12877,7 +12904,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12886,7 +12913,7 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>102</v>
@@ -12895,10 +12922,10 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>20</v>
@@ -12909,13 +12936,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>20</v>
@@ -12937,13 +12964,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12994,7 +13021,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13006,16 +13033,16 @@
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>20</v>
@@ -13026,10 +13053,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13141,10 +13168,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13258,14 +13285,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13287,16 +13314,16 @@
         <v>135</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13345,7 +13372,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13377,14 +13404,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13406,16 +13433,16 @@
         <v>157</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13425,7 +13452,7 @@
         <v>20</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>20</v>
@@ -13464,7 +13491,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13482,10 +13509,10 @@
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>20</v>
@@ -13496,10 +13523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13525,16 +13552,16 @@
         <v>233</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13544,7 +13571,7 @@
         <v>20</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>20</v>
@@ -13565,7 +13592,7 @@
         <v>239</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -13583,7 +13610,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13592,7 +13619,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -13604,7 +13631,7 @@
         <v>242</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>20</v>
@@ -13615,10 +13642,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13641,17 +13668,17 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13700,7 +13727,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13718,24 +13745,24 @@
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13758,16 +13785,16 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13817,7 +13844,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13838,7 +13865,7 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>20</v>
@@ -13849,10 +13876,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13878,13 +13905,13 @@
         <v>121</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13934,7 +13961,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13943,7 +13970,7 @@
         <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>102</v>
@@ -13952,10 +13979,10 @@
         <v>20</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>20</v>
@@ -13966,10 +13993,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13995,16 +14022,16 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14032,10 +14059,10 @@
         <v>176</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -14053,7 +14080,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14071,7 +14098,7 @@
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>161</v>
@@ -14080,15 +14107,15 @@
         <v>20</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14114,16 +14141,16 @@
         <v>233</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14151,10 +14178,10 @@
         <v>115</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -14172,7 +14199,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14181,7 +14208,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -14190,10 +14217,10 @@
         <v>20</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>20</v>
@@ -14204,10 +14231,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14230,16 +14257,16 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14289,7 +14316,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14298,7 +14325,7 @@
         <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
@@ -14307,10 +14334,10 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>20</v>
@@ -14321,10 +14348,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14350,16 +14377,16 @@
         <v>233</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14387,37 +14414,37 @@
         <v>115</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z104" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI104" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>102</v>
@@ -14426,10 +14453,10 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>20</v>
@@ -14440,10 +14467,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14469,13 +14496,13 @@
         <v>80</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14525,7 +14552,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14534,7 +14561,7 @@
         <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>102</v>
@@ -14543,10 +14570,10 @@
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>20</v>
@@ -14557,13 +14584,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>20</v>
@@ -14585,13 +14612,13 @@
         <v>20</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14642,7 +14669,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14654,16 +14681,16 @@
         <v>20</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>20</v>
@@ -14674,10 +14701,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14789,10 +14816,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14906,14 +14933,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14935,16 +14962,16 @@
         <v>135</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -14993,7 +15020,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15025,14 +15052,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15054,16 +15081,16 @@
         <v>157</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -15073,7 +15100,7 @@
         <v>20</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>20</v>
@@ -15112,7 +15139,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15130,10 +15157,10 @@
         <v>20</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>20</v>
@@ -15144,10 +15171,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15173,16 +15200,16 @@
         <v>233</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15192,7 +15219,7 @@
         <v>20</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>20</v>
@@ -15213,7 +15240,7 @@
         <v>239</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -15231,7 +15258,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15240,7 +15267,7 @@
         <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>102</v>
@@ -15252,7 +15279,7 @@
         <v>242</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>20</v>
@@ -15263,10 +15290,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15289,17 +15316,17 @@
         <v>20</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15348,7 +15375,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15366,24 +15393,24 @@
         <v>20</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15406,16 +15433,16 @@
         <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15465,7 +15492,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15486,7 +15513,7 @@
         <v>20</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>20</v>
@@ -15497,10 +15524,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15526,13 +15553,13 @@
         <v>121</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15582,7 +15609,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15591,7 +15618,7 @@
         <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>102</v>
@@ -15600,10 +15627,10 @@
         <v>20</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>20</v>
@@ -15614,10 +15641,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15643,16 +15670,16 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -15680,10 +15707,10 @@
         <v>176</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>20</v>
@@ -15701,7 +15728,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15719,7 +15746,7 @@
         <v>20</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>161</v>
@@ -15728,15 +15755,15 @@
         <v>20</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15762,16 +15789,16 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15799,10 +15826,10 @@
         <v>115</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>20</v>
@@ -15820,7 +15847,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15829,7 +15856,7 @@
         <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>102</v>
@@ -15838,10 +15865,10 @@
         <v>20</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>20</v>
@@ -15852,10 +15879,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15878,16 +15905,16 @@
         <v>20</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15937,7 +15964,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15946,7 +15973,7 @@
         <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>102</v>
@@ -15955,10 +15982,10 @@
         <v>20</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>20</v>
@@ -15969,10 +15996,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15998,16 +16025,16 @@
         <v>233</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -16035,37 +16062,37 @@
         <v>115</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z118" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>102</v>
@@ -16074,10 +16101,10 @@
         <v>20</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>20</v>
@@ -16088,10 +16115,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16117,13 +16144,13 @@
         <v>80</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16173,7 +16200,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16182,7 +16209,7 @@
         <v>79</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>102</v>
@@ -16191,10 +16218,10 @@
         <v>20</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>20</v>
@@ -16205,13 +16232,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>20</v>
@@ -16233,13 +16260,13 @@
         <v>20</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16290,7 +16317,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16302,16 +16329,16 @@
         <v>20</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>20</v>
@@ -16322,10 +16349,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16437,10 +16464,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16554,14 +16581,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16583,16 +16610,16 @@
         <v>135</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -16641,7 +16668,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16673,14 +16700,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16702,16 +16729,16 @@
         <v>157</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -16721,7 +16748,7 @@
         <v>20</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>20</v>
@@ -16760,7 +16787,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16778,10 +16805,10 @@
         <v>20</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>20</v>
@@ -16792,10 +16819,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16821,16 +16848,16 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16840,7 +16867,7 @@
         <v>20</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>20</v>
@@ -16861,7 +16888,7 @@
         <v>239</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>20</v>
@@ -16879,7 +16906,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16888,7 +16915,7 @@
         <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>102</v>
@@ -16900,7 +16927,7 @@
         <v>242</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>20</v>
@@ -16911,10 +16938,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16937,17 +16964,17 @@
         <v>20</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>20</v>
@@ -16996,7 +17023,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17014,24 +17041,24 @@
         <v>20</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17054,16 +17081,16 @@
         <v>20</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17113,7 +17140,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17134,7 +17161,7 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>20</v>
@@ -17145,10 +17172,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17174,13 +17201,13 @@
         <v>121</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17230,7 +17257,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17239,7 +17266,7 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
@@ -17248,10 +17275,10 @@
         <v>20</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>20</v>
@@ -17262,10 +17289,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17291,16 +17318,16 @@
         <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
@@ -17328,10 +17355,10 @@
         <v>176</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>20</v>
@@ -17349,7 +17376,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17367,7 +17394,7 @@
         <v>20</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>161</v>
@@ -17376,15 +17403,15 @@
         <v>20</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17410,16 +17437,16 @@
         <v>233</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -17447,10 +17474,10 @@
         <v>115</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>20</v>
@@ -17468,7 +17495,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17477,7 +17504,7 @@
         <v>90</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>102</v>
@@ -17486,10 +17513,10 @@
         <v>20</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>20</v>
@@ -17500,10 +17527,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17526,16 +17553,16 @@
         <v>20</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17585,7 +17612,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17594,7 +17621,7 @@
         <v>79</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>102</v>
@@ -17603,10 +17630,10 @@
         <v>20</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>20</v>
@@ -17617,10 +17644,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17646,16 +17673,16 @@
         <v>233</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -17683,37 +17710,37 @@
         <v>115</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z132" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI132" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>102</v>
@@ -17722,10 +17749,10 @@
         <v>20</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>20</v>
@@ -17736,10 +17763,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17765,13 +17792,13 @@
         <v>80</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17821,7 +17848,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17830,7 +17857,7 @@
         <v>79</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>102</v>
@@ -17839,10 +17866,10 @@
         <v>20</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>20</v>
@@ -17853,13 +17880,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>20</v>
@@ -17881,13 +17908,13 @@
         <v>20</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17938,7 +17965,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17950,16 +17977,16 @@
         <v>20</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>20</v>
@@ -17970,10 +17997,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18085,10 +18112,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18202,14 +18229,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18231,16 +18258,16 @@
         <v>135</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>166</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>20</v>
@@ -18289,7 +18316,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18321,14 +18348,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18350,16 +18377,16 @@
         <v>157</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -18369,7 +18396,7 @@
         <v>20</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>20</v>
@@ -18408,7 +18435,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18426,10 +18453,10 @@
         <v>20</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>20</v>
@@ -18440,10 +18467,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18469,16 +18496,16 @@
         <v>233</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -18488,7 +18515,7 @@
         <v>20</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>20</v>
@@ -18509,7 +18536,7 @@
         <v>239</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>20</v>
@@ -18527,7 +18554,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18536,7 +18563,7 @@
         <v>90</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>102</v>
@@ -18548,7 +18575,7 @@
         <v>242</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>20</v>
@@ -18559,10 +18586,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18585,17 +18612,17 @@
         <v>20</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -18644,7 +18671,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18662,24 +18689,24 @@
         <v>20</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18702,16 +18729,16 @@
         <v>20</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18761,7 +18788,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18782,7 +18809,7 @@
         <v>20</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>20</v>
@@ -18793,10 +18820,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18822,13 +18849,13 @@
         <v>121</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18878,7 +18905,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18887,7 +18914,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -18896,10 +18923,10 @@
         <v>20</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>20</v>
@@ -18910,10 +18937,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18939,16 +18966,16 @@
         <v>110</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>20</v>
@@ -18976,10 +19003,10 @@
         <v>176</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>20</v>
@@ -18997,7 +19024,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19015,7 +19042,7 @@
         <v>20</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>161</v>
@@ -19024,15 +19051,15 @@
         <v>20</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>450</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19058,16 +19085,16 @@
         <v>233</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -19095,10 +19122,10 @@
         <v>115</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>20</v>
@@ -19116,7 +19143,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19125,7 +19152,7 @@
         <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>102</v>
@@ -19134,10 +19161,10 @@
         <v>20</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>20</v>
@@ -19148,10 +19175,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19174,16 +19201,16 @@
         <v>20</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19233,7 +19260,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19242,7 +19269,7 @@
         <v>79</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>102</v>
@@ -19251,10 +19278,10 @@
         <v>20</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>20</v>
@@ -19265,10 +19292,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19294,16 +19321,16 @@
         <v>233</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -19331,37 +19358,37 @@
         <v>115</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="Z146" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI146" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>102</v>
@@ -19370,10 +19397,10 @@
         <v>20</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>242</v>
+        <v>479</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>20</v>
@@ -19384,10 +19411,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19413,13 +19440,13 @@
         <v>80</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19469,7 +19496,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19478,7 +19505,7 @@
         <v>79</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>102</v>
@@ -19487,10 +19514,10 @@
         <v>20</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTC-Composition-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-Composition-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-Composition-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-Composition-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
